--- a/Ostalo/Cjenik studio 031 Alma 010926.xlsx
+++ b/Ostalo/Cjenik studio 031 Alma 010926.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\KalkulacijeGradjevina\Ostalo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{608F664C-A696-4286-9BA2-703A1791EFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E32F3F-292A-4C14-8C08-B1808EE845FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2610" yWindow="645" windowWidth="26190" windowHeight="14835" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Radnja" sheetId="1" r:id="rId1"/>
@@ -132,13 +132,13 @@
     <t>Uređivanje polu duge brade:</t>
   </si>
   <si>
-    <t>Moderno frizure</t>
-  </si>
-  <si>
     <t>Dana 1.09.2026.</t>
   </si>
   <si>
     <t>Fed bez izbrijavanja</t>
+  </si>
+  <si>
+    <t>Moderne frizure</t>
   </si>
 </sst>
 </file>
@@ -357,13 +357,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperveza" xfId="2" builtinId="8"/>
@@ -781,7 +781,7 @@
     </row>
     <row r="9" spans="2:8" ht="22.5" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -820,7 +820,7 @@
     </row>
     <row r="12" spans="2:8" ht="22.5" x14ac:dyDescent="0.35">
       <c r="B12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -998,7 +998,7 @@
     </row>
     <row r="26" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B26" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -1011,12 +1011,12 @@
     <row r="27" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="2:9" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
     </row>
     <row r="30" spans="2:9" ht="21" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
@@ -1061,11 +1061,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="str">
+      <c r="A1" s="28" t="str">
         <f>Radnja!B8</f>
         <v>Cjenik:</v>
       </c>
-      <c r="B1" s="27"/>
+      <c r="B1" s="28"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -1073,21 +1073,21 @@
       <c r="G1" s="8"/>
       <c r="H1" s="9"/>
       <c r="I1" s="8"/>
-      <c r="J1" s="27" t="str">
+      <c r="J1" s="28" t="str">
         <f>A1</f>
         <v>Cjenik:</v>
       </c>
-      <c r="K1" s="27"/>
+      <c r="K1" s="28"/>
     </row>
     <row r="2" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="F2" s="10"/>
       <c r="I2" s="8"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
     </row>
     <row r="3" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
@@ -1116,15 +1116,15 @@
     <row r="4" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="str">
         <f>Radnja!B9</f>
-        <v>Moderno frizure</v>
+        <v>Moderne frizure</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
-      <c r="D4" s="26" t="e">
+      <c r="D4" s="27" t="e">
         <f>Radnja!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E4" s="26"/>
+      <c r="E4" s="27"/>
       <c r="F4" s="15"/>
       <c r="G4" s="16">
         <f>Radnja!F9</f>
@@ -1134,7 +1134,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="13" t="str">
         <f t="shared" ref="J4:J15" si="1">A4</f>
-        <v>Moderno frizure</v>
+        <v>Moderne frizure</v>
       </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
@@ -1668,11 +1668,11 @@
       <c r="I29" s="8"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="str">
+      <c r="A30" s="28" t="str">
         <f>A1</f>
         <v>Cjenik:</v>
       </c>
-      <c r="B30" s="27"/>
+      <c r="B30" s="28"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
@@ -1680,21 +1680,21 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="27" t="str">
+      <c r="J30" s="28" t="str">
         <f>A30</f>
         <v>Cjenik:</v>
       </c>
-      <c r="K30" s="27"/>
+      <c r="K30" s="28"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="27"/>
-      <c r="B31" s="27"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="F31" s="10"/>
       <c r="I31" s="8"/>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="28"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
@@ -1725,15 +1725,15 @@
     <row r="33" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="str">
         <f t="shared" ref="A33:A44" si="5">A4</f>
-        <v>Moderno frizure</v>
+        <v>Moderne frizure</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
-      <c r="D33" s="26" t="e">
+      <c r="D33" s="27" t="e">
         <f>D4</f>
         <v>#REF!</v>
       </c>
-      <c r="E33" s="26"/>
+      <c r="E33" s="27"/>
       <c r="F33" s="15"/>
       <c r="G33" s="16">
         <f t="shared" si="3"/>
@@ -1743,7 +1743,7 @@
       <c r="I33" s="8"/>
       <c r="J33" s="13" t="str">
         <f t="shared" ref="J33:J44" si="6">A33</f>
-        <v>Moderno frizure</v>
+        <v>Moderne frizure</v>
       </c>
       <c r="K33" s="14"/>
       <c r="L33" s="14"/>
